--- a/data/gold/results/uncertainty_summary.xlsx
+++ b/data/gold/results/uncertainty_summary.xlsx
@@ -113,18 +113,18 @@
     <t>visitor +/-20%</t>
   </si>
   <si>
+    <t>anaesthetic +/-50%</t>
+  </si>
+  <si>
     <t>pmdi +/-50%</t>
   </si>
   <si>
-    <t>anaesthetic +/-50%</t>
+    <t>anaesthetic +/-20%</t>
   </si>
   <si>
     <t>pmdi +/-20%</t>
   </si>
   <si>
-    <t>anaesthetic +/-20%</t>
-  </si>
-  <si>
     <t>P(rank 1)</t>
   </si>
   <si>
@@ -137,30 +137,30 @@
     <t>Contribution</t>
   </si>
   <si>
+    <t>Pharmaceuticals and chemical products</t>
+  </si>
+  <si>
+    <t>Food and food services</t>
+  </si>
+  <si>
+    <t>Heat and electricity</t>
+  </si>
+  <si>
+    <t>Individual travel</t>
+  </si>
+  <si>
+    <t>Medical, electrical equipment and machinery</t>
+  </si>
+  <si>
+    <t>Operational impacts</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
     <t>Transport</t>
   </si>
   <si>
-    <t>Food and food services</t>
-  </si>
-  <si>
-    <t>Heat and electricity</t>
-  </si>
-  <si>
-    <t>Individual travel</t>
-  </si>
-  <si>
-    <t>Medical, electrical equipment and machinery</t>
-  </si>
-  <si>
-    <t>Operational impacts</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals and chemical products</t>
-  </si>
-  <si>
-    <t>Services</t>
-  </si>
-  <si>
     <t>Unallocated</t>
   </si>
   <si>
@@ -191,7 +191,7 @@
     <t>official emission accounts; alpha-proration of industry 880000 and medical-N2O netting</t>
   </si>
   <si>
-    <t>2019 expenditure on a 2016-price table: Danish net price index 2016-&gt;2019 ~ +3.5%; sampled around the deflated level</t>
+    <t>nowcast intensity vs 2022 price inflation (DST coupled-models report pp. 21-22)</t>
   </si>
   <si>
     <t>waste extension = 2011 hybrid-EXIOBASE absolute account on 2016 monetary output (Steenmeijer precedent); vintage+classification mismatch</t>
@@ -560,28 +560,28 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>4628.122062700192</v>
+        <v>1853.911685255345</v>
       </c>
       <c r="C2">
-        <v>754.1175523753257</v>
+        <v>1339.915588010944</v>
       </c>
       <c r="D2">
-        <v>180.5321341518415</v>
+        <v>921.1918622629997</v>
       </c>
       <c r="E2">
-        <v>150.9246439492933</v>
+        <v>129.4847557754865</v>
       </c>
       <c r="F2">
         <v>12.7</v>
       </c>
       <c r="G2">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="H2">
-        <v>327.9446</v>
+        <v>363.7266</v>
       </c>
       <c r="I2">
-        <v>225.9423</v>
+        <v>242.5114</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -589,13 +589,13 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1840.176537998628</v>
+        <v>1861.983933522006</v>
       </c>
       <c r="C3">
-        <v>1129.661499993992</v>
+        <v>2924.042064732495</v>
       </c>
       <c r="D3">
-        <v>134.3999160586708</v>
+        <v>781.6681210452316</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>14.9206776551314</v>
+        <v>16.518404287656</v>
       </c>
       <c r="I3">
-        <v>10.2798223448686</v>
+        <v>11.013495712344</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -618,13 +618,13 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>38.07090316673552</v>
+        <v>16.23503612216632</v>
       </c>
       <c r="C4">
-        <v>17.08442410567785</v>
+        <v>20.05719459529767</v>
       </c>
       <c r="D4">
-        <v>2.161480724022677</v>
+        <v>6.536304608046691</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -636,10 +636,10 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0.103613761220928</v>
+        <v>0.1146548933917042</v>
       </c>
       <c r="I4">
-        <v>0.07138623877907203</v>
+        <v>0.07644510660829575</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -647,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>2647.618898275895</v>
+        <v>1653.666331477455</v>
       </c>
       <c r="C5">
-        <v>752.9042888256793</v>
+        <v>1646.700904396185</v>
       </c>
       <c r="D5">
-        <v>113.2403207432043</v>
+        <v>531.0508450829358</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0.9713642094803109</v>
+        <v>1.075392103167403</v>
       </c>
       <c r="I5">
-        <v>0.6692357905196892</v>
+        <v>0.7170078968325971</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -676,16 +676,16 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>542.2225145110635</v>
+        <v>505.5047532986458</v>
       </c>
       <c r="C6">
-        <v>220.7972212611156</v>
+        <v>700.9609017771467</v>
       </c>
       <c r="D6">
-        <v>57.17950625212023</v>
+        <v>230.2355918181278</v>
       </c>
       <c r="E6">
-        <v>247.2010724959712</v>
+        <v>45.1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -741,25 +741,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>5842.246269149928</v>
+        <v>4407.008017325768</v>
       </c>
       <c r="C2">
-        <v>5973.48505443341</v>
+        <v>4580.102847460387</v>
       </c>
       <c r="D2">
-        <v>6122.336424014062</v>
+        <v>4772.844151291929</v>
       </c>
       <c r="E2">
-        <v>6280.216054842776</v>
+        <v>4974.740111579384</v>
       </c>
       <c r="F2">
-        <v>6451.631264549525</v>
+        <v>5189.322456966074</v>
       </c>
       <c r="G2">
-        <v>-4.574889967913509</v>
+        <v>-7.664950339246568</v>
       </c>
       <c r="H2">
-        <v>5.378581275668681</v>
+        <v>8.725998429288984</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -767,25 +767,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>2910.899908359788</v>
+        <v>5029.849846243142</v>
       </c>
       <c r="C3">
-        <v>2966.581293676328</v>
+        <v>5225.087436776102</v>
       </c>
       <c r="D3">
-        <v>3024.674165993522</v>
+        <v>5428.713761537667</v>
       </c>
       <c r="E3">
-        <v>3084.10301500577</v>
+        <v>5640.91693880539</v>
       </c>
       <c r="F3">
-        <v>3143.82654474035</v>
+        <v>5861.026804002939</v>
       </c>
       <c r="G3">
-        <v>-3.761537652977665</v>
+        <v>-7.347300535910895</v>
       </c>
       <c r="H3">
-        <v>3.9393459330747</v>
+        <v>7.963452512972813</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>53.4399948807769</v>
+        <v>38.66892377304921</v>
       </c>
       <c r="C4">
-        <v>54.48381254244742</v>
+        <v>40.16977074956833</v>
       </c>
       <c r="D4">
-        <v>55.54838220864116</v>
+        <v>41.73778304520646</v>
       </c>
       <c r="E4">
-        <v>56.63453941087229</v>
+        <v>43.36785174206086</v>
       </c>
       <c r="F4">
-        <v>57.74144677601448</v>
+        <v>45.0649092146766</v>
       </c>
       <c r="G4">
-        <v>-3.795587277312773</v>
+        <v>-7.352712693995622</v>
       </c>
       <c r="H4">
-        <v>3.948025991353132</v>
+        <v>7.97149711058327</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -819,25 +819,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>3267.179677203668</v>
+        <v>3443.828480251047</v>
       </c>
       <c r="C5">
-        <v>3330.56694606972</v>
+        <v>3577.714697128629</v>
       </c>
       <c r="D5">
-        <v>3395.599576127732</v>
+        <v>3717.498995338165</v>
       </c>
       <c r="E5">
-        <v>3462.270391570278</v>
+        <v>3863.562561094168</v>
       </c>
       <c r="F5">
-        <v>3530.306022208725</v>
+        <v>4015.485930024753</v>
       </c>
       <c r="G5">
-        <v>-3.781950611223461</v>
+        <v>-7.361683632740911</v>
       </c>
       <c r="H5">
-        <v>3.96708867052602</v>
+        <v>8.015790590939531</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -845,25 +845,25 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>602.7220306098681</v>
+        <v>672.4780771524333</v>
       </c>
       <c r="C6">
-        <v>776.1422266025655</v>
+        <v>974.5778520473846</v>
       </c>
       <c r="D6">
-        <v>1041.765808242027</v>
+        <v>1439.4843092981</v>
       </c>
       <c r="E6">
-        <v>1437.300005946362</v>
+        <v>2140.813196619004</v>
       </c>
       <c r="F6">
-        <v>2023.454305270191</v>
+        <v>3172.761417179925</v>
       </c>
       <c r="G6">
-        <v>-42.1441915408073</v>
+        <v>-53.28340345159185</v>
       </c>
       <c r="H6">
-        <v>94.2331269908691</v>
+        <v>120.4095867308883</v>
       </c>
     </row>
   </sheetData>
@@ -895,13 +895,13 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>-204.5683868219894</v>
+        <v>-295.3396344505982</v>
       </c>
       <c r="C2">
-        <v>212.6642787305154</v>
+        <v>318.9381456358642</v>
       </c>
       <c r="D2">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -909,13 +909,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>-109.1022172019948</v>
+        <v>-117.1030454977217</v>
       </c>
       <c r="C3">
-        <v>210.9790176401611</v>
+        <v>226.4508103995577</v>
       </c>
       <c r="D3">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -923,13 +923,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>-116.176593975425</v>
+        <v>-128.8526096366941</v>
       </c>
       <c r="C4">
-        <v>179.9114387289083</v>
+        <v>199.5415564396362</v>
       </c>
       <c r="D4">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -937,13 +937,13 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>-163.9722999999994</v>
+        <v>-181.8633</v>
       </c>
       <c r="C5">
-        <v>163.9723000000004</v>
+        <v>181.8633</v>
       </c>
       <c r="D5">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -951,13 +951,13 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>-112.9711499999994</v>
+        <v>-121.2557000000006</v>
       </c>
       <c r="C6">
-        <v>112.9711500000003</v>
+        <v>121.2556999999997</v>
       </c>
       <c r="D6">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -965,13 +965,13 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>-65.58892000000014</v>
+        <v>-72.74531999999999</v>
       </c>
       <c r="C7">
-        <v>65.58892000000014</v>
+        <v>72.74531999999999</v>
       </c>
       <c r="D7">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -979,13 +979,13 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>-45.1884599999994</v>
+        <v>-48.50228000000061</v>
       </c>
       <c r="C8">
-        <v>45.1884600000003</v>
+        <v>48.5022799999997</v>
       </c>
       <c r="D8">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -993,13 +993,13 @@
         <v>3</v>
       </c>
       <c r="B9">
-        <v>-25.71667025323131</v>
+        <v>-22.06343960776303</v>
       </c>
       <c r="C9">
-        <v>30.99865916648378</v>
+        <v>26.59508551094041</v>
       </c>
       <c r="D9">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1013,7 +1013,7 @@
         <v>8.538732229321795</v>
       </c>
       <c r="D10">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1021,13 +1021,13 @@
         <v>30</v>
       </c>
       <c r="B11">
-        <v>-6.400000000000546</v>
+        <v>-6.349999999999454</v>
       </c>
       <c r="C11">
-        <v>6.399999999999636</v>
+        <v>6.350000000000364</v>
       </c>
       <c r="D11">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1035,13 +1035,13 @@
         <v>31</v>
       </c>
       <c r="B12">
-        <v>-6.349999999999454</v>
+        <v>-5.800000000000182</v>
       </c>
       <c r="C12">
-        <v>6.350000000000364</v>
+        <v>5.799999999999272</v>
       </c>
       <c r="D12">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1049,13 +1049,13 @@
         <v>5</v>
       </c>
       <c r="B13">
-        <v>-3.067052345336378</v>
+        <v>-2.779516187961235</v>
       </c>
       <c r="C13">
-        <v>4.033543733433362</v>
+        <v>3.655399008423956</v>
       </c>
       <c r="D13">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1063,13 +1063,13 @@
         <v>32</v>
       </c>
       <c r="B14">
-        <v>-2.5600000000004</v>
+        <v>-2.539999999999964</v>
       </c>
       <c r="C14">
-        <v>2.559999999999491</v>
+        <v>2.539999999999964</v>
       </c>
       <c r="D14">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1077,13 +1077,13 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <v>-2.539999999999964</v>
+        <v>-2.320000000000618</v>
       </c>
       <c r="C15">
-        <v>2.539999999999964</v>
+        <v>2.319999999999709</v>
       </c>
       <c r="D15">
-        <v>6103.949053702921</v>
+        <v>4751.591317238897</v>
       </c>
     </row>
   </sheetData>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0.0117</v>
+        <v>0.0248</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1192,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.9752</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.9743000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1243,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.9883</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.0117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>0.1827</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1285,7 +1285,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -1399,12 +1399,12 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
         <v>1</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -1481,10 +1481,10 @@
         <v>0</v>
       </c>
       <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
         <v>1</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -1569,12 +1569,12 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -1705,12 +1705,12 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -1739,12 +1739,12 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -1795,33 +1795,33 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50">
-        <v>0.5966</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0.4031</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51">
-        <v>0.4034</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0.5966</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
@@ -1838,15 +1838,15 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>0.9997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -1880,7 +1880,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1987,25 +1987,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>5334.593545180323</v>
+        <v>3508.574149484324</v>
       </c>
       <c r="C2">
-        <v>5480.044068677852</v>
+        <v>3695.637753987759</v>
       </c>
       <c r="D2">
-        <v>5648.202782372047</v>
+        <v>3918.048183230789</v>
       </c>
       <c r="E2">
-        <v>5845.29637657804</v>
+        <v>4195.847011266804</v>
       </c>
       <c r="F2">
-        <v>6055.489166835212</v>
+        <v>4532.136446873954</v>
       </c>
       <c r="G2">
-        <v>-5.552372131016514</v>
+        <v>-10.45096983490428</v>
       </c>
       <c r="H2">
-        <v>7.21090230213226</v>
+        <v>15.67332087112805</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2013,25 +2013,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1972.512700813475</v>
+        <v>2684.806175037397</v>
       </c>
       <c r="C3">
-        <v>2025.423659588598</v>
+        <v>2828.370269057436</v>
       </c>
       <c r="D3">
-        <v>2093.315926869623</v>
+        <v>3007.713681163792</v>
       </c>
       <c r="E3">
-        <v>2177.631401941599</v>
+        <v>3234.37758652204</v>
       </c>
       <c r="F3">
-        <v>2302.055793380259</v>
+        <v>3563.969445360266</v>
       </c>
       <c r="G3">
-        <v>-5.77090273405596</v>
+        <v>-10.73597889814598</v>
       </c>
       <c r="H3">
-        <v>9.971732590922787</v>
+        <v>18.49430574725581</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2039,25 +2039,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>41.44525801415953</v>
+        <v>25.09675090804485</v>
       </c>
       <c r="C4">
-        <v>43.6614742827099</v>
+        <v>27.71263389924293</v>
       </c>
       <c r="D4">
-        <v>48.53235321850747</v>
+        <v>33.43780503003558</v>
       </c>
       <c r="E4">
-        <v>53.3579994414202</v>
+        <v>39.14797148096013</v>
       </c>
       <c r="F4">
-        <v>55.69834900588979</v>
+        <v>42.19011114909676</v>
       </c>
       <c r="G4">
-        <v>-14.60282622694942</v>
+        <v>-24.94498103119617</v>
       </c>
       <c r="H4">
-        <v>14.76539939268722</v>
+        <v>26.17488232615566</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2065,25 +2065,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>2755.00101187827</v>
+        <v>2333.748186350419</v>
       </c>
       <c r="C5">
-        <v>2870.039590974812</v>
+        <v>2563.588238463987</v>
       </c>
       <c r="D5">
-        <v>3079.678563284116</v>
+        <v>3023.118687356774</v>
       </c>
       <c r="E5">
-        <v>3298.684471641215</v>
+        <v>3502.197985991328</v>
       </c>
       <c r="F5">
-        <v>3422.649188310519</v>
+        <v>3773.120398752432</v>
       </c>
       <c r="G5">
-        <v>-10.54257919240815</v>
+        <v>-22.80328932798523</v>
       </c>
       <c r="H5">
-        <v>11.1365721447457</v>
+        <v>24.80887417792428</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2091,25 +2091,25 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>555.6538538328606</v>
+        <v>502.8348824994488</v>
       </c>
       <c r="C6">
-        <v>709.9362723350307</v>
+        <v>754.6278721633269</v>
       </c>
       <c r="D6">
-        <v>947.4291331198779</v>
+        <v>1139.958698109159</v>
       </c>
       <c r="E6">
-        <v>1306.275357881005</v>
+        <v>1730.440860079152</v>
       </c>
       <c r="F6">
-        <v>1830.434773602889</v>
+        <v>2601.646252192373</v>
       </c>
       <c r="G6">
-        <v>-41.35140725479951</v>
+        <v>-55.89007888325275</v>
       </c>
       <c r="H6">
-        <v>93.20017821019286</v>
+        <v>128.2228519776818</v>
       </c>
     </row>
   </sheetData>
@@ -2141,41 +2141,41 @@
         <v>47</v>
       </c>
       <c r="B2">
-        <v>-133.1370247897667</v>
+        <v>-237.5373163971544</v>
       </c>
       <c r="C2">
-        <v>294.7347721860169</v>
+        <v>525.8530220616303</v>
       </c>
       <c r="D2">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>-109.1022172019939</v>
+        <v>-231.2281172782873</v>
       </c>
       <c r="C3">
-        <v>210.9790176401611</v>
+        <v>249.7039284307266</v>
       </c>
       <c r="D3">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>-186.0801681044059</v>
+        <v>-117.1030454977213</v>
       </c>
       <c r="C4">
-        <v>193.4443799002611</v>
+        <v>226.4508103995586</v>
       </c>
       <c r="D4">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2183,13 +2183,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>-116.176593975425</v>
+        <v>-128.8526096366945</v>
       </c>
       <c r="C5">
-        <v>179.9114387289083</v>
+        <v>199.5415564396362</v>
       </c>
       <c r="D5">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2197,13 +2197,13 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-163.9722999999994</v>
+        <v>-181.8633</v>
       </c>
       <c r="C6">
-        <v>163.9723000000004</v>
+        <v>181.8633</v>
       </c>
       <c r="D6">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2211,13 +2211,13 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-112.9711499999994</v>
+        <v>-121.2556999999997</v>
       </c>
       <c r="C7">
-        <v>112.9711500000003</v>
+        <v>121.2557000000002</v>
       </c>
       <c r="D7">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2225,13 +2225,13 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>-65.58892000000014</v>
+        <v>-72.74531999999999</v>
       </c>
       <c r="C8">
-        <v>65.58892000000014</v>
+        <v>72.74531999999999</v>
       </c>
       <c r="D8">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2239,13 +2239,13 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>-45.1884599999994</v>
+        <v>-48.5022799999997</v>
       </c>
       <c r="C9">
-        <v>45.1884600000003</v>
+        <v>48.50228000000016</v>
       </c>
       <c r="D9">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2253,13 +2253,13 @@
         <v>3</v>
       </c>
       <c r="B10">
-        <v>-25.71667025323131</v>
+        <v>-22.06343960776303</v>
       </c>
       <c r="C10">
-        <v>30.99865916648378</v>
+        <v>26.59508551094041</v>
       </c>
       <c r="D10">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2267,13 +2267,13 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>-5.105855572804103</v>
+        <v>-5.105855572804558</v>
       </c>
       <c r="C11">
         <v>8.538732229321795</v>
       </c>
       <c r="D11">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2281,13 +2281,13 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>-6.400000000000546</v>
+        <v>-6.349999999999909</v>
       </c>
       <c r="C12">
-        <v>6.399999999999636</v>
+        <v>6.350000000000364</v>
       </c>
       <c r="D12">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2295,13 +2295,13 @@
         <v>31</v>
       </c>
       <c r="B13">
-        <v>-6.349999999999454</v>
+        <v>-5.799999999999727</v>
       </c>
       <c r="C13">
-        <v>6.350000000000364</v>
+        <v>5.800000000000182</v>
       </c>
       <c r="D13">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2309,13 +2309,13 @@
         <v>5</v>
       </c>
       <c r="B14">
-        <v>-3.067052345336378</v>
+        <v>-2.779516187961235</v>
       </c>
       <c r="C14">
-        <v>4.033543733433362</v>
+        <v>3.655399008424411</v>
       </c>
       <c r="D14">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2323,13 +2323,13 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>-2.5600000000004</v>
+        <v>-2.539999999999964</v>
       </c>
       <c r="C15">
-        <v>2.559999999999491</v>
+        <v>2.539999999999964</v>
       </c>
       <c r="D15">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2337,13 +2337,13 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>-2.539999999999964</v>
+        <v>-2.319999999999709</v>
       </c>
       <c r="C16">
-        <v>2.539999999999964</v>
+        <v>2.320000000000164</v>
       </c>
       <c r="D16">
-        <v>5618.297349973212</v>
+        <v>3885.112570325153</v>
       </c>
     </row>
   </sheetData>
@@ -2375,58 +2375,58 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8052</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.1891</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>0.1751</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.5349</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.2475</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>0.0197</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.2672</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -2435,15 +2435,15 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0.7156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.06759999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2503,10 +2503,10 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.9897</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="E10">
-        <v>0.2065</v>
+        <v>0.2118</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2545,16 +2545,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0.8598</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>0.1402</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2562,16 +2562,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.1402</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.8598</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -2656,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0.2865</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0.6842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2673,15 +2673,15 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0.7135</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0.2865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0.0293</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2715,16 +2715,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>0.9457</v>
+        <v>0.999</v>
       </c>
       <c r="D26">
-        <v>0.0543</v>
+        <v>0.001</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2732,24 +2732,24 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.0543</v>
+        <v>0.001</v>
       </c>
       <c r="D27">
-        <v>0.4888</v>
+        <v>0.999</v>
       </c>
       <c r="E27">
-        <v>0.3652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -2761,12 +2761,12 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -2826,15 +2826,15 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0.4569</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0.5431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0.0917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2885,33 +2885,33 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0.9715</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.0284</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.0285</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.9715</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -2962,15 +2962,15 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -2979,15 +2979,15 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0.355</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0.3632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -2996,15 +2996,15 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0.645</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0.355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0.2818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3055,36 +3055,36 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50">
-        <v>0.9676</v>
+        <v>0.9756</v>
       </c>
       <c r="D50">
-        <v>0.0321</v>
+        <v>0.0244</v>
       </c>
       <c r="E50">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51">
-        <v>0.0323</v>
+        <v>0.0244</v>
       </c>
       <c r="D51">
-        <v>0.2989</v>
+        <v>0.9756</v>
       </c>
       <c r="E51">
-        <v>0.3069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -3095,13 +3095,13 @@
         <v>12</v>
       </c>
       <c r="C52">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0.669</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>0.3309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3140,7 +3140,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
@@ -3169,12 +3169,12 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0.3619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -3203,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3290,13 +3290,13 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="C7" t="s">
         <v>56</v>
       </c>
       <c r="D7">
-        <v>0.966</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="8" spans="1:4">
